--- a/tests/data_golden/errors.template.xlsx
+++ b/tests/data_golden/errors.template.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
   <si>
     <t>errors-type-mismatch-num</t>
   </si>
